--- a/artfynd/A 23584-2024 artfynd.xlsx
+++ b/artfynd/A 23584-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1145,10 +1145,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111233024</v>
+        <v>111234306</v>
       </c>
       <c r="B6" t="n">
-        <v>44331</v>
+        <v>44338</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,26 +1161,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>201164</v>
+        <v>102021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sexfläckig bastardsvärmare</t>
+          <t>Mindre bastardsvärmare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Zygaena filipendulae</t>
+          <t>Zygaena viciae</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr"/>
@@ -1267,10 +1267,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111234306</v>
+        <v>83956485</v>
       </c>
       <c r="B7" t="n">
-        <v>44338</v>
+        <v>58046</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1279,33 +1279,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102021</v>
+        <v>103044</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre bastardsvärmare</t>
+          <t>Grönsiska</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Zygaena viciae</t>
+          <t>Spinus spinus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
@@ -1316,10 +1315,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>348695.661856762</v>
+        <v>348696</v>
       </c>
       <c r="R7" t="n">
-        <v>6431628.231396855</v>
+        <v>6431628</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1346,22 +1345,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2020-03-29</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-08-02</t>
+          <t>2020-03-29</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,7 +1369,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1382,242 +1380,10 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Björn Albinson, Tony Norman</t>
+          <t>Björn Albinson, Somkid Phueakphan</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="n">
-        <v>118492598</v>
-      </c>
-      <c r="B8" t="n">
-        <v>44530</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>102021</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Mindre bastardsvärmare</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Zygaena viciae</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>(Denis &amp; Schiffermüller, 1775)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Grusgropen Antens kapell,Alingsås, Vg</t>
-        </is>
-      </c>
-      <c r="Q8" t="n">
-        <v>348696</v>
-      </c>
-      <c r="R8" t="n">
-        <v>6431628</v>
-      </c>
-      <c r="S8" t="n">
-        <v>25</v>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Alingsås</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>Långared</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2024-07-16</t>
-        </is>
-      </c>
-      <c r="AD8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="inlineStr"/>
-      <c r="AG8" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>Björn Albinson</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>Björn Albinson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="n">
-        <v>83956485</v>
-      </c>
-      <c r="B9" t="n">
-        <v>58046</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>103044</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Grönsiska</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Spinus spinus</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Grusgropen Antens kapell,Alingsås, Vg</t>
-        </is>
-      </c>
-      <c r="Q9" t="n">
-        <v>348696</v>
-      </c>
-      <c r="R9" t="n">
-        <v>6431628</v>
-      </c>
-      <c r="S9" t="n">
-        <v>25</v>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Alingsås</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>Långared</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>2020-03-29</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>2020-03-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AD9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT9" t="inlineStr"/>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>Björn Albinson</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>Björn Albinson, Somkid Phueakphan</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
